--- a/uploads/reviews.xlsx
+++ b/uploads/reviews.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zish0\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECFF683-11B4-4DC3-A22E-9B48191F072F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2906B4-0B81-4733-9E96-F9123156AF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,27 +25,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>review</t>
   </si>
   <si>
-    <t>I love this product</t>
-  </si>
-  <si>
-    <t>this is not good product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nice product but costly </t>
-  </si>
-  <si>
-    <t xml:space="preserve">product is far away from my budget but it is very helpful </t>
-  </si>
-  <si>
     <t xml:space="preserve">your overall service is very good </t>
   </si>
   <si>
-    <t xml:space="preserve">I am very satisfied with this product </t>
+    <t>I love this mobile</t>
+  </si>
+  <si>
+    <t>this is not good laptop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nice laptop but costly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mobile is far away from my budget but it is very helpful </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am very satisfied with this laptop </t>
+  </si>
+  <si>
+    <t>the design of this mobile is good</t>
+  </si>
+  <si>
+    <t>the design of this laptop is not good</t>
+  </si>
+  <si>
+    <t>I amm happy to purchacse this mobile</t>
+  </si>
+  <si>
+    <t>is is bad experience to use this mobile</t>
+  </si>
+  <si>
+    <t>your productt is not good at all</t>
+  </si>
+  <si>
+    <t>I will not take your services next time</t>
+  </si>
+  <si>
+    <t>your products are ugly</t>
+  </si>
+  <si>
+    <t>you products are bad</t>
   </si>
 </sst>
 </file>
@@ -363,10 +387,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
+    <col min="1" max="1" width="72.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -376,32 +400,72 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
